--- a/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +83,11 @@
       <name val="Calibri"/>
       <color rgb="00999999"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="12">
@@ -174,69 +182,80 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="24">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="8" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="9" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="10" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="11" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -596,15 +615,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -612,6 +632,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -640,9 +661,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -671,8 +690,25 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -681,18 +717,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -709,6 +745,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -867,6 +904,7 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -1044,6 +1082,7 @@
       <c r="F21" s="11" t="n"/>
       <c r="G21" s="13" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
@@ -1163,6 +1202,26 @@
       <c r="E28" s="12" t="n"/>
       <c r="F28" s="11" t="n"/>
       <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C29">
+        <f>COUNTIF(E6:E28,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E29">
+        <f>COUNTIF(B6:B28,"?*")</f>
+        <v>19.0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
@@ -1188,12 +1247,26 @@
     <mergeCell ref="A23:G23"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G28">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E21 E25 E26 E27 E28" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E21 E25 E26 E27 E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1202,18 +1275,18 @@
   <sheetPr>
     <tabColor rgb="00EFEBE9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1230,6 +1303,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1369,6 +1443,7 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="13" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
@@ -1527,6 +1602,7 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
@@ -1647,6 +1723,26 @@
       <c r="F26" s="11" t="n"/>
       <c r="G26" s="13" t="n"/>
     </row>
+    <row r="27">
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C27">
+        <f>COUNTIF(E6:E26,"✓")</f>
+        <v>2.0</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E27">
+        <f>COUNTIF(B6:B26,"?*")</f>
+        <v>17.0</v>
+      </c>
+    </row>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
@@ -1664,18 +1760,32 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A28:G28"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A29:G29"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G26">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E23 E24 E25 E26" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E23 E24 E25 E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -692,9 +692,45 @@
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Higiene y temperaturas:</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ La primera sección de «Apertura» es de higiene personal y de arranque seguro: extracción primero, comprobación del gas después (si lo tienes) y sólo entonces temperadora, vitrinas y climatización.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ Las cámaras no se «encienden»: se comprueba que han funcionado toda la noche y se anota la lectura. Objetivos de este oficio: obrador 18-20 °C, conservación 15-18 °C con 50-60 % de humedad, rellenos y ganaches 0-4 °C, vitrina de bombonería 16-18 °C.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>▸ Por encima de 20 °C la manteca de cacao empieza a fundir: el bombón suda, pierde brillo y en dos días aparece el fat bloom. Es la razón de que la vitrina lleve su propio control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -719,7 +755,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -749,7 +785,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Encendido y verificación de equipos</t>
+          <t>Higiene personal y arranque seguro del obrador</t>
         </is>
       </c>
     </row>
@@ -796,12 +832,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Encender temperadora de chocolate y precalentar a 45°C</t>
+          <t>Uniforme y calzado de trabajo limpios, delantal cambiado y pelo recogido bajo gorro o redecilla</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Templado</t>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D6" s="11" t="n"/>
@@ -815,12 +851,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Verificar cámara de conservación a 15-18°C (bombones)</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Conservación</t>
+          <t>Sin anillos, pulseras, reloj ni pendientes colgantes; uñas cortas, limpias y sin esmalte ni postizos</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -834,12 +870,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Verificar nevera de rellenos y ganaches a 4°C</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
-        <is>
-          <t>Cámara</t>
+          <t>Lavado de manos con jabón y secado con papel de un solo uso, y otra vez en cada cambio de tarea (el chocolate acabado ya no lleva ningún paso que destruya patógenos)</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -853,12 +889,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Encender iluminación de vitrina y sala de tienda</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Vitrina</t>
+          <t>Heridas y cortes cubiertos con apósito impermeable de color visible y guante encima</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -872,12 +908,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Encender aire acondicionado — mantener sala 20-22°C</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>Tienda</t>
+          <t>Quien tenga vómitos, diarrea, fiebre o lesiones cutáneas infectadas NO manipula producto: comunicarlo al encargado y reasignar tarea</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -891,12 +927,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Registrar temperaturas en hoja de control APPCC</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Encender la extracción del obrador ANTES que ningún otro equipo</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
@@ -904,11 +940,29 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Si el obrador tiene instalación de gas (fogón, marmita o quemador): comprobar que no hay olor, abrir la llave general y sólo después encender los equipos</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Obrador</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="13" t="n"/>
+    </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Montaje de servicio</t>
+          <t>Encendido y verificación de equipos</t>
         </is>
       </c>
     </row>
@@ -955,12 +1009,12 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Montar vitrina: bombones, tabletas, figuras, trufas</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Vitrina</t>
+          <t>Encender temperadora de chocolate y precalentar a 45 °C</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Templado</t>
         </is>
       </c>
       <c r="D15" s="11" t="n"/>
@@ -974,12 +1028,12 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Verificar etiquetado de alérgenos en cada producto expuesto</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Vitrina</t>
+          <t>Comprobar que la cámara de conservación ha funcionado toda la noche (sin cortes ni alarmas) y registrar la temperatura: objetivo 15-18 °C y 50-60 % de humedad — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Conservación</t>
         </is>
       </c>
       <c r="D16" s="11" t="n"/>
@@ -993,12 +1047,12 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Reponer bolsas, cajas regalo, papel de seda, cintas</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Packaging</t>
+          <t>Comprobar que la nevera de rellenos y ganaches ha funcionado toda la noche y registrar la temperatura: objetivo 0-4 °C — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Cámara</t>
         </is>
       </c>
       <c r="D17" s="11" t="n"/>
@@ -1012,12 +1066,12 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Verificar stock de cajas de bombones surtidos</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>Packaging</t>
+          <t>Encender iluminación de vitrina y sala de tienda</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
         </is>
       </c>
       <c r="D18" s="11" t="n"/>
@@ -1031,12 +1085,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Preparar zona de degustación con muestras del día</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Mostrador</t>
+          <t>Comprobar que la vitrina de bombonería mantiene 16-18 °C y no condensa antes de montar el género (por encima de 20 °C la manteca de cacao funde y el bombón pierde brillo) — anota la lectura: ____ °C</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
         </is>
       </c>
       <c r="D19" s="11" t="n"/>
@@ -1050,12 +1104,12 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Activar TPV y verificar fondo de caja</t>
+          <t>Encender aire acondicionado — mantener sala 20-22 °C</t>
         </is>
       </c>
       <c r="C20" s="16" t="inlineStr">
         <is>
-          <t>Caja</t>
+          <t>Tienda</t>
         </is>
       </c>
       <c r="D20" s="11" t="n"/>
@@ -1069,12 +1123,12 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Colocar pizarra con novedades y productos destacados</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Tienda</t>
+          <t>Registrar las temperaturas de obrador, cámara y nevera: si tienes el Pack APPCC, en su hoja de temperaturas; si no, aquí mismo en «Notas»</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D21" s="11" t="n"/>
@@ -1086,7 +1140,7 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Verificaciones finales</t>
+          <t>Montaje de servicio</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1187,12 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Comprobar que música ambiental funciona</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>Tienda</t>
+          <t>Montar vitrina: bombones, tabletas, figuras, trufas</t>
+        </is>
+      </c>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
         </is>
       </c>
       <c r="D25" s="11" t="n"/>
@@ -1152,7 +1206,7 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Verificar limpieza de cristales de vitrina</t>
+          <t>Verificar el etiquetado de cada producto expuesto: denominación, precio (y precio por kilo si se vende al peso) y los alérgenos declarados — leche, frutos secos, soja, gluten, huevo y sésamo— más las trazas</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -1171,12 +1225,12 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Confirmar pedidos online pendientes de preparar</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Reponer bolsas, cajas regalo, papel de seda, cintas</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="D27" s="11" t="n"/>
@@ -1190,12 +1244,12 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Revisar agenda: pedidos especiales, eventos, encargos</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Verificar stock de cajas de bombones surtidos</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Packaging</t>
         </is>
       </c>
       <c r="D28" s="11" t="n"/>
@@ -1204,57 +1258,236 @@
       <c r="G28" s="13" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="23" t="inlineStr">
+      <c r="A29" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Preparar zona de degustación con muestras del día</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Mostrador</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="13" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar que el TPV está activo y que el fondo de caja ya se ha contado y anotado antes de abrir la puerta: el recuento no se repite aquí, se hace en «Apertura de Caja» del fichero 09 (hito en 08/09)</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Caja</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="13" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Colocar pizarra con novedades y productos destacados</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="13" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Verificaciones finales</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar que música ambiental funciona</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>Tienda</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Verificar limpieza de cristales de vitrina</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>Vitrina</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Confirmar pedidos online pendientes de preparar</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="13" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Revisar agenda: pedidos especiales, eventos, encargos</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="13" t="n"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="23" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C29">
-        <f>COUNTIF(E6:E28,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="C39">
+        <f>COUNTIFS(B6:B38,"?*",E6:E38,"✓")-COUNTIFS(B6:B38,"Tarea",E6:E38,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E29">
-        <f>COUNTIF(B6:B28,"?*")</f>
-        <v>19.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="E39">
+        <f>COUNTIF(B6:B38,"?*")-COUNTIF(B6:B38,"Tarea")-COUNTIF(E6:E38,"N/A")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A41:G41"/>
     <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G28">
+  <conditionalFormatting sqref="A6:G38">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E15 E16 E17 E18 E19 E20 E21 E25 E26 E27 E28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E15 E16 E17 E18 E19 E20 E21 E25 E26 E27 E28 E29 E30 E31 E35 E36 E37 E38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1277,7 +1510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1625,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Cuadre de caja y registro de ventas del día</t>
+          <t>Comprobar que el arqueo del día ha quedado cerrado y firmado y las ventas registradas: el cuadre no se repite aquí, se hace en «Cierre de Caja» del fichero 09 (hito en 08/09)</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -1411,7 +1644,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Apagar TPV y cerrar terminal de pago</t>
+          <t>Comprobar que el TPV y el terminal de pago quedan cerrados DESPUÉS del arqueo, nunca antes: el cierre de terminal se manda en «Cierre del Negocio» del fichero 08 (hito en 08/09)</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
@@ -1551,7 +1784,7 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Verificar temperaturas de cámaras y registrar</t>
+          <t>Comprobar y registrar las temperaturas antes de cerrar: cámara de conservación 15-18 °C y nevera de rellenos 0-4 °C — anota las lecturas: ____ °C / ____ °C</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -1589,12 +1822,12 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Barrer y fregar suelo de obrador</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Anotar las mermas del día: producto, cantidad y motivo (rotura, mal templado, bloom, caducidad, degustación o prueba)</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D19" s="11" t="n"/>
@@ -1602,77 +1835,77 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="13" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Barrer y fregar suelo de obrador</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Seguridad y cierre</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Tarea</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>Zona</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>Hora</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t>Apagar equipos excepto cámaras y neveras</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Verificar que gas, agua y luces quedan apagadas</t>
+          <t>Apagar equipos excepto cámaras y neveras</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -1687,16 +1920,16 @@
     </row>
     <row r="25">
       <c r="A25" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Sacar basura y reciclar cartón/plástico</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>Limpieza</t>
+          <t>Cerrar la llave general de gas si el obrador la tiene y verificar que agua y luces quedan apagadas</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>General</t>
         </is>
       </c>
       <c r="D25" s="11" t="n"/>
@@ -1706,16 +1939,16 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Activar alarma y cerrar con llave</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>General</t>
+          <t>Sacar basura y reciclar cartón/plástico</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Limpieza</t>
         </is>
       </c>
       <c r="D26" s="11" t="n"/>
@@ -1724,57 +1957,76 @@
       <c r="G26" s="13" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="23" t="inlineStr">
+      <c r="A27" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Activar alarma y cerrar con llave</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C27">
-        <f>COUNTIF(E6:E26,"✓")</f>
-        <v>2.0</v>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="C28">
+        <f>COUNTIFS(B6:B27,"?*",E6:E27,"✓")-COUNTIFS(B6:B27,"Tarea",E6:E27,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E27">
-        <f>COUNTIF(B6:B26,"?*")</f>
-        <v>17.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E28">
+        <f>COUNTIF(B6:B27,"?*")-COUNTIF(B6:B27,"Tarea")-COUNTIF(E6:E27,"N/A")</f>
+        <v>16.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A22:G22"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G26">
+  <conditionalFormatting sqref="A6:G27">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E23 E24 E25 E26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E14 E15 E16 E17 E18 E19 E20 E24 E25 E26 E27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/01-apertura-cierre.xlsx
@@ -617,7 +617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2012,8 +2012,8 @@
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A29:G29"/>
